--- a/Import_Inventory/6.คลังผลิต.xlsx
+++ b/Import_Inventory/6.คลังผลิต.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="262">
   <si>
     <t>partner_id</t>
   </si>
@@ -46,30 +46,769 @@
     <t>sequence</t>
   </si>
   <si>
-    <t>MOGEN_OB</t>
-  </si>
-  <si>
-    <t>คลังผลิต</t>
-  </si>
-  <si>
-    <t>PD01/Stock</t>
-  </si>
-  <si>
-    <t>NFG06-JIG-002</t>
-  </si>
-  <si>
     <t>date</t>
   </si>
   <si>
-    <t>PD01-OB</t>
+    <t>MOG-OB</t>
+  </si>
+  <si>
+    <t>PCJ0011815</t>
+  </si>
+  <si>
+    <t>MO TO FG10</t>
+  </si>
+  <si>
+    <t>FG10/Stock</t>
+  </si>
+  <si>
+    <t>MS00901001</t>
+  </si>
+  <si>
+    <t>PCJ0011816</t>
+  </si>
+  <si>
+    <t>FU00043DE811511</t>
+  </si>
+  <si>
+    <t>PCJ0011819</t>
+  </si>
+  <si>
+    <t>MO00001A0S10000</t>
+  </si>
+  <si>
+    <t>MO00050A0010000</t>
+  </si>
+  <si>
+    <t>MO0038S1211</t>
+  </si>
+  <si>
+    <t>MO00691117</t>
+  </si>
+  <si>
+    <t>MO0079S0111</t>
+  </si>
+  <si>
+    <t>MO049EXS1210</t>
+  </si>
+  <si>
+    <t>MT0081SA0010000</t>
+  </si>
+  <si>
+    <t>MT057EXS1210</t>
+  </si>
+  <si>
+    <t>OJ00076876</t>
+  </si>
+  <si>
+    <t>NX5WB0006114</t>
+  </si>
+  <si>
+    <t>OJ00076877</t>
+  </si>
+  <si>
+    <t>NX5SWH0002100</t>
+  </si>
+  <si>
+    <t>OJ00076878</t>
+  </si>
+  <si>
+    <t>VT00AC0311</t>
+  </si>
+  <si>
+    <t>OJ00076879</t>
+  </si>
+  <si>
+    <t>SP00284100</t>
+  </si>
+  <si>
+    <t>NX5SP66100</t>
+  </si>
+  <si>
+    <t>OJ00076880</t>
+  </si>
+  <si>
+    <t>NX5RS0008101</t>
+  </si>
+  <si>
+    <t>OJ00076881</t>
+  </si>
+  <si>
+    <t>NX5FCA0008100</t>
+  </si>
+  <si>
+    <t>NXSP205100</t>
+  </si>
+  <si>
+    <t>NXSP127100</t>
+  </si>
+  <si>
+    <t>OJ00076882</t>
+  </si>
+  <si>
+    <t>NXSP024100</t>
+  </si>
+  <si>
+    <t>NX5FCA0001100</t>
+  </si>
+  <si>
+    <t>NX5FCA0006100</t>
+  </si>
+  <si>
+    <t>NX5SP129100</t>
+  </si>
+  <si>
+    <t>OJ00076883</t>
+  </si>
+  <si>
+    <t>OJ00076884</t>
+  </si>
+  <si>
+    <t>NX4MM0104001</t>
+  </si>
+  <si>
+    <t>OJ00076885</t>
+  </si>
+  <si>
+    <t>NX4MM097001</t>
+  </si>
+  <si>
+    <t>OJ00076886</t>
+  </si>
+  <si>
+    <t>NXMM17E600</t>
+  </si>
+  <si>
+    <t>OJ00076889</t>
+  </si>
+  <si>
+    <t>NX4MM0019103</t>
+  </si>
+  <si>
+    <t>OJ00076856</t>
+  </si>
+  <si>
+    <t>MO049E1210</t>
+  </si>
+  <si>
+    <t>OJ00076921</t>
+  </si>
+  <si>
+    <t>MT00441210</t>
+  </si>
+  <si>
+    <t>OJ00076918</t>
+  </si>
+  <si>
+    <t>MT0034B+101</t>
+  </si>
+  <si>
+    <t>PCJ0011823</t>
+  </si>
+  <si>
+    <t>MA142P101</t>
+  </si>
+  <si>
+    <t>PCJ0011824</t>
+  </si>
+  <si>
+    <t>OJ00076930</t>
+  </si>
+  <si>
+    <t>MO015S101</t>
+  </si>
+  <si>
+    <t>OJ00076929</t>
+  </si>
+  <si>
+    <t>MO15SS101</t>
+  </si>
+  <si>
+    <t>OJ00076932</t>
+  </si>
+  <si>
+    <t>MO0069S1101</t>
+  </si>
+  <si>
+    <t>OJ00076945</t>
+  </si>
+  <si>
+    <t>MA0094201</t>
+  </si>
+  <si>
+    <t>PCJ0011900</t>
+  </si>
+  <si>
+    <t>MSP016500</t>
+  </si>
+  <si>
+    <t>PCJ0011901</t>
+  </si>
+  <si>
+    <t>SPV0005100</t>
+  </si>
+  <si>
+    <t>NX5SBS0005100</t>
+  </si>
+  <si>
+    <t>PCJ0011902</t>
+  </si>
+  <si>
+    <t>SPW41N1100</t>
+  </si>
+  <si>
+    <t>PCJ0011904</t>
+  </si>
+  <si>
+    <t>SPW41N2100</t>
+  </si>
+  <si>
+    <t>SPW41N3100</t>
+  </si>
+  <si>
+    <t>SPW41N4100</t>
+  </si>
+  <si>
+    <t>PCJ0011903</t>
+  </si>
+  <si>
+    <t>OJ00076948</t>
+  </si>
+  <si>
+    <t>MA332B1101</t>
+  </si>
+  <si>
+    <t>OJ00076951</t>
+  </si>
+  <si>
+    <t>LA0213263</t>
+  </si>
+  <si>
+    <t>OJ00076952</t>
+  </si>
+  <si>
+    <t>OJ00076956</t>
+  </si>
+  <si>
+    <t>NX4FP0500D7L97A</t>
+  </si>
+  <si>
+    <t>OJ00076953</t>
+  </si>
+  <si>
+    <t>NX4FU0033FC1560</t>
+  </si>
+  <si>
+    <t>OJ00076954</t>
+  </si>
+  <si>
+    <t>NX4FM0500D7R99A</t>
+  </si>
+  <si>
+    <t>OJ00076955</t>
+  </si>
+  <si>
+    <t>NX4FP0500D7R99A</t>
+  </si>
+  <si>
+    <t>OJ00076949</t>
+  </si>
+  <si>
+    <t>MA266B201</t>
+  </si>
+  <si>
+    <t>OJ00076950</t>
+  </si>
+  <si>
+    <t>OJ00076957</t>
+  </si>
+  <si>
+    <t>OJ00076958</t>
+  </si>
+  <si>
+    <t>OJ00076959</t>
+  </si>
+  <si>
+    <t>NX5WB0007110</t>
+  </si>
+  <si>
+    <t>OJ00076960</t>
+  </si>
+  <si>
+    <t>NX4FU0018FC03</t>
+  </si>
+  <si>
+    <t>OJ00076961</t>
+  </si>
+  <si>
+    <t>NXMAC0181C11</t>
+  </si>
+  <si>
+    <t>OJ00076962</t>
+  </si>
+  <si>
+    <t>NX4LA21DGR1500</t>
+  </si>
+  <si>
+    <t>OJ00076963</t>
+  </si>
+  <si>
+    <t>MA0351101</t>
+  </si>
+  <si>
+    <t>OJ00076964</t>
+  </si>
+  <si>
+    <t>MA0572R110</t>
+  </si>
+  <si>
+    <t>OJ00076965</t>
+  </si>
+  <si>
+    <t>MA183A101</t>
+  </si>
+  <si>
+    <t>OJ00076985</t>
+  </si>
+  <si>
+    <t>NX20002I0010000</t>
+  </si>
+  <si>
+    <t>PCJ0011907</t>
+  </si>
+  <si>
+    <t>FU0033FC1560</t>
+  </si>
+  <si>
+    <t>PCJ0011910</t>
+  </si>
+  <si>
+    <t>NX40026DF012024</t>
+  </si>
+  <si>
+    <t>PCJ0011909</t>
+  </si>
+  <si>
+    <t>NX40028DDC12000</t>
+  </si>
+  <si>
+    <t>PCJ0011908</t>
+  </si>
+  <si>
+    <t>NX40054DKL10500</t>
+  </si>
+  <si>
+    <t>OJ00076991</t>
+  </si>
+  <si>
+    <t>NX40008DFC12709</t>
+  </si>
+  <si>
+    <t>OJ00076999</t>
+  </si>
+  <si>
+    <t>SPW013100</t>
+  </si>
+  <si>
+    <t>OJ00076995</t>
+  </si>
+  <si>
+    <t>MO050H0C10000</t>
+  </si>
+  <si>
+    <t>OJ00076997</t>
+  </si>
+  <si>
+    <t>SPW051100</t>
+  </si>
+  <si>
+    <t>OJ00076998</t>
+  </si>
+  <si>
+    <t>SPW012100</t>
+  </si>
+  <si>
+    <t>OJ00076996</t>
+  </si>
+  <si>
+    <t>SPW014100</t>
+  </si>
+  <si>
+    <t>OJ00076993</t>
+  </si>
+  <si>
+    <t>SPWO11100</t>
+  </si>
+  <si>
+    <t>PCJ0011913</t>
+  </si>
+  <si>
+    <t>AC0061101</t>
+  </si>
+  <si>
+    <t>OJ00077002</t>
+  </si>
+  <si>
+    <t>ERS0026110</t>
+  </si>
+  <si>
+    <t>OJ00077003</t>
+  </si>
+  <si>
+    <t>MAM011C118</t>
+  </si>
+  <si>
+    <t>OJ00077004</t>
+  </si>
+  <si>
+    <t>OJ00077005</t>
+  </si>
+  <si>
+    <t>MA266P201</t>
+  </si>
+  <si>
+    <t>PCJ0011915</t>
+  </si>
+  <si>
+    <t>PCJ0011916</t>
+  </si>
+  <si>
+    <t>SP00212100</t>
+  </si>
+  <si>
+    <t>OJ00077025</t>
+  </si>
+  <si>
+    <t>ERS0002110</t>
+  </si>
+  <si>
+    <t>OJ00077023</t>
+  </si>
+  <si>
+    <t>ERS0029100</t>
+  </si>
+  <si>
+    <t>OJ00077021</t>
+  </si>
+  <si>
+    <t>SPW261100</t>
+  </si>
+  <si>
+    <t>OJ00077020</t>
+  </si>
+  <si>
+    <t>SPW262100</t>
+  </si>
+  <si>
+    <t>OJ00077036</t>
+  </si>
+  <si>
+    <t>MA0142101</t>
+  </si>
+  <si>
+    <t>VT0142B101</t>
+  </si>
+  <si>
+    <t>VT0142P101</t>
+  </si>
+  <si>
+    <t>OJ00077044</t>
+  </si>
+  <si>
+    <t>SP0024100</t>
+  </si>
+  <si>
+    <t>OJ00077047</t>
+  </si>
+  <si>
+    <t>AC0052101</t>
+  </si>
+  <si>
+    <t>OJ00077053</t>
+  </si>
+  <si>
+    <t>SPW19N110</t>
+  </si>
+  <si>
+    <t>OJ00077052</t>
+  </si>
+  <si>
+    <t>SPU004100</t>
+  </si>
+  <si>
+    <t>PCJ0011941</t>
+  </si>
+  <si>
+    <t>PCJ0011923</t>
+  </si>
+  <si>
+    <t>MA142B101</t>
+  </si>
+  <si>
+    <t>PCJ0011926</t>
+  </si>
+  <si>
+    <t>PCJ0011927</t>
+  </si>
+  <si>
+    <t>PCJ0011928</t>
+  </si>
+  <si>
+    <t>OJ00077060</t>
+  </si>
+  <si>
+    <t>MO042S101</t>
+  </si>
+  <si>
+    <t>OJ00077070</t>
+  </si>
+  <si>
+    <t>NX5ERS0031130</t>
+  </si>
+  <si>
+    <t>OJ00077071</t>
+  </si>
+  <si>
+    <t>NX5ML0088100</t>
+  </si>
+  <si>
+    <t>OJ00077072</t>
+  </si>
+  <si>
+    <t>NX5MSP023200</t>
+  </si>
+  <si>
+    <t>OJ00077073</t>
+  </si>
+  <si>
+    <t>OJ00077061</t>
+  </si>
+  <si>
+    <t>FU000F113535</t>
+  </si>
+  <si>
+    <t>OJ00077062</t>
+  </si>
+  <si>
+    <t>OJ00077063</t>
+  </si>
+  <si>
+    <t>FU000F11105</t>
+  </si>
+  <si>
+    <t>OJ00077064</t>
+  </si>
+  <si>
+    <t>OJ00077065</t>
+  </si>
+  <si>
+    <t>MA0362101</t>
+  </si>
+  <si>
+    <t>OJ00077066</t>
+  </si>
+  <si>
+    <t>MA0523C110</t>
+  </si>
+  <si>
+    <t>OJ00077068</t>
+  </si>
+  <si>
+    <t>MAM011C116</t>
+  </si>
+  <si>
+    <t>OJ00077069</t>
+  </si>
+  <si>
+    <t>MAM011C115</t>
+  </si>
+  <si>
+    <t>OJ00077074</t>
+  </si>
+  <si>
+    <t>NX4FO0019LC770</t>
+  </si>
+  <si>
+    <t>OJ00077075</t>
+  </si>
+  <si>
+    <t>NX40FUDE8L11500</t>
+  </si>
+  <si>
+    <t>OJ00077076</t>
+  </si>
+  <si>
+    <t>OJ00077077</t>
+  </si>
+  <si>
+    <t>NX4F00018FC12</t>
+  </si>
+  <si>
+    <t>OJ00077082</t>
+  </si>
+  <si>
+    <t>FCA0096100</t>
+  </si>
+  <si>
+    <t>PCJ0011982</t>
+  </si>
+  <si>
+    <t>MO42ES1710</t>
+  </si>
+  <si>
+    <t>OJ00077087</t>
+  </si>
+  <si>
+    <t>MA00001B0010000</t>
+  </si>
+  <si>
+    <t>OJ00077091</t>
+  </si>
+  <si>
+    <t>MT00681110</t>
+  </si>
+  <si>
+    <t>OJ00077099</t>
+  </si>
+  <si>
+    <t>SWH006100</t>
+  </si>
+  <si>
+    <t>OJ00077094</t>
+  </si>
+  <si>
+    <t>MT411S101</t>
+  </si>
+  <si>
+    <t>OJ00077086</t>
+  </si>
+  <si>
+    <t>SPW0403100</t>
+  </si>
+  <si>
+    <t>PCJ0011988</t>
+  </si>
+  <si>
+    <t>PCJ0011987</t>
+  </si>
+  <si>
+    <t>PCJ0011998</t>
+  </si>
+  <si>
+    <t>ACS4825SP120</t>
+  </si>
+  <si>
+    <t>PCJ0011994</t>
+  </si>
+  <si>
+    <t>NX0MAM0BDC10000</t>
+  </si>
+  <si>
+    <t>PCJ0011995</t>
+  </si>
+  <si>
+    <t>MO031N101A</t>
+  </si>
+  <si>
+    <t>PCJ0011996</t>
+  </si>
+  <si>
+    <t>OJ00077116</t>
+  </si>
+  <si>
+    <t>MO0050EX1210</t>
+  </si>
+  <si>
+    <t>OJ00077102</t>
+  </si>
+  <si>
+    <t>OJ00077103</t>
+  </si>
+  <si>
+    <t>MA092B101</t>
+  </si>
+  <si>
+    <t>OJ00077104</t>
+  </si>
+  <si>
+    <t>OJ00077105</t>
+  </si>
+  <si>
+    <t>MA0154101</t>
+  </si>
+  <si>
+    <t>OJ00077106</t>
+  </si>
+  <si>
+    <t>MA0054101</t>
+  </si>
+  <si>
+    <t>OJ00077111</t>
+  </si>
+  <si>
+    <t>FU0025HC19</t>
+  </si>
+  <si>
+    <t>OJ00077112</t>
+  </si>
+  <si>
+    <t>FU00043DEC21511</t>
+  </si>
+  <si>
+    <t>OJ00077108</t>
+  </si>
+  <si>
+    <t>VTMAE0201</t>
+  </si>
+  <si>
+    <t>OJ00077109</t>
+  </si>
+  <si>
+    <t>NX4FU043BQL160</t>
+  </si>
+  <si>
+    <t>OJ00077110</t>
+  </si>
+  <si>
+    <t>NX4MF015R1Q4</t>
+  </si>
+  <si>
+    <t>PCJ0011999</t>
+  </si>
+  <si>
+    <t>MO0830ADC10000</t>
+  </si>
+  <si>
+    <t>OJ00077135</t>
+  </si>
+  <si>
+    <t>MT055B+101</t>
+  </si>
+  <si>
+    <t>OJ00077138</t>
+  </si>
+  <si>
+    <t>MT20SS101</t>
+  </si>
+  <si>
+    <t>PCJ0012000</t>
+  </si>
+  <si>
+    <t>MT00431210</t>
+  </si>
+  <si>
+    <t>OJ00077142</t>
+  </si>
+  <si>
+    <t>OJ00077141</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="[$-1070000]d/m/yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -113,11 +852,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma 2" xfId="1"/>
@@ -423,23 +1163,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K161"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="19.8" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="9.109375" style="1"/>
+    <col min="2" max="2" width="15.21875" style="4" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" style="1"/>
+    <col min="4" max="4" width="13.33203125" style="4" customWidth="1"/>
+    <col min="5" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -461,45 +1205,4652 @@
         <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.5">
       <c r="A2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="4">
+        <v>45992</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="4">
+        <v>45992</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="3">
+        <v>2</v>
+      </c>
+      <c r="I2" s="3">
+        <v>539.36874999999998</v>
+      </c>
+      <c r="K2" s="2"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.5">
+      <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="4">
+        <v>45992</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="4">
+        <v>45992</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="1">
+        <v>5</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1998.3592400000002</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.5">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="4">
+        <v>45993</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="4">
+        <v>45993</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1">
+        <v>6170.0427</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.5">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="4">
+        <v>45993</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="4">
+        <v>45993</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="1">
+        <v>1</v>
+      </c>
+      <c r="I5" s="1">
+        <v>2949.3789000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.5">
+      <c r="A6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="4">
+        <v>45993</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="4">
+        <v>45993</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1">
+        <v>2714.2094999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.5">
+      <c r="A7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="4">
+        <v>45993</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="4">
+        <v>45993</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H7" s="1">
+        <v>1</v>
+      </c>
+      <c r="I7" s="1">
+        <v>2091.5526</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.5">
+      <c r="A8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="4">
+        <v>45993</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="4">
+        <v>45993</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1624.7787000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.5">
+      <c r="A9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="4">
+        <v>45993</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="4">
+        <v>45993</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9" s="1">
+        <v>1</v>
+      </c>
+      <c r="I9" s="1">
+        <v>2734.7228</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.5">
+      <c r="A10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="4">
+        <v>45993</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="4">
+        <v>45993</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" s="1">
+        <v>1</v>
+      </c>
+      <c r="I10" s="1">
+        <v>1501.8424</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.5">
+      <c r="A11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="4">
+        <v>45993</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="4">
+        <v>45993</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H11" s="1">
+        <v>1</v>
+      </c>
+      <c r="I11" s="1">
+        <v>1272.4219000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.5">
+      <c r="A12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4">
+        <v>45993</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="4">
+        <v>45993</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H12" s="1">
+        <v>1</v>
+      </c>
+      <c r="I12" s="1">
+        <v>203.5676</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.5">
+      <c r="A13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="4">
+        <v>45993</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" s="4">
+        <v>45993</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H13" s="1">
+        <v>1</v>
+      </c>
+      <c r="I13" s="1">
+        <v>370.27789999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.5">
+      <c r="A14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="4">
+        <v>45993</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" s="4">
+        <v>45993</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H14" s="1">
+        <v>1</v>
+      </c>
+      <c r="I14" s="1">
+        <v>321.51220000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.5">
+      <c r="A15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="4">
+        <v>45993</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="4">
+        <v>45993</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H15" s="1">
+        <v>1</v>
+      </c>
+      <c r="I15" s="1">
+        <v>109.88160000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.5">
+      <c r="A16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" s="4">
+        <v>45993</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" s="4">
+        <v>45993</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H16" s="1">
+        <v>1</v>
+      </c>
+      <c r="I16" s="1">
+        <v>280.13260000000002</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" s="4">
+        <v>45993</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" s="4">
+        <v>45993</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H17" s="1">
+        <v>1</v>
+      </c>
+      <c r="I17" s="1">
+        <v>309.52440000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" s="4">
+        <v>45993</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D18" s="4">
+        <v>45993</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H18" s="1">
+        <v>2</v>
+      </c>
+      <c r="I18" s="1">
+        <v>435.41325000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A19" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" s="4">
+        <v>45993</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D19" s="4">
+        <v>45993</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H19" s="1">
+        <v>1</v>
+      </c>
+      <c r="I19" s="1">
+        <v>373.31360000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A20" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20" s="4">
+        <v>45993</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D20" s="4">
+        <v>45993</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H20" s="1">
+        <v>1</v>
+      </c>
+      <c r="I20" s="1">
+        <v>499.78879999999998</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21" s="4">
+        <v>45993</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D21" s="4">
+        <v>45993</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H21" s="1">
+        <v>1</v>
+      </c>
+      <c r="I21" s="1">
+        <v>210.5153</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A22" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" s="4">
+        <v>45993</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D22" s="4">
+        <v>45993</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H22" s="1">
+        <v>1</v>
+      </c>
+      <c r="I22" s="1">
+        <v>436.58780000000002</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A23" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23" s="4">
+        <v>45993</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D23" s="4">
+        <v>45993</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H23" s="1">
+        <v>1</v>
+      </c>
+      <c r="I23" s="1">
+        <v>455.08150000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A24" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24" s="4">
+        <v>45993</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D24" s="4">
+        <v>45993</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H24" s="1">
+        <v>1</v>
+      </c>
+      <c r="I24" s="1">
+        <v>531.53309999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A25" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25" s="4">
+        <v>45993</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D25" s="4">
+        <v>45993</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H25" s="1">
+        <v>5</v>
+      </c>
+      <c r="I25" s="1">
+        <v>183.01241999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A26" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26" s="4">
+        <v>45993</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D26" s="4">
+        <v>45993</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H26" s="1">
+        <v>1</v>
+      </c>
+      <c r="I26" s="1">
+        <v>437.71879999999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A27" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27" s="4">
+        <v>45993</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D27" s="4">
+        <v>45993</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H27" s="1">
+        <v>1</v>
+      </c>
+      <c r="I27" s="1">
+        <v>995.57600000000002</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A28" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28" s="4">
+        <v>45993</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D28" s="4">
+        <v>45993</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H28" s="1">
+        <v>1</v>
+      </c>
+      <c r="I28" s="1">
+        <v>2308.9200999999998</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A29" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29" s="4">
+        <v>45993</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D29" s="4">
+        <v>45993</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H29" s="1">
+        <v>1</v>
+      </c>
+      <c r="I29" s="1">
+        <v>394.47919999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A30" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B30" s="4">
+        <v>45993</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D30" s="4">
+        <v>45993</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H30" s="1">
+        <v>1</v>
+      </c>
+      <c r="I30" s="1">
+        <v>2195.7188000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A31" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B31" s="4">
+        <v>45993</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D31" s="4">
+        <v>45993</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H31" s="1">
+        <v>1</v>
+      </c>
+      <c r="I31" s="1">
+        <v>7465.0609000000004</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A32" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32" s="4">
+        <v>45995</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D32" s="4">
+        <v>45995</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H32" s="1">
+        <v>14</v>
+      </c>
+      <c r="I32" s="1">
+        <v>2166.2826142857143</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A33" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B33" s="4">
+        <v>45995</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D33" s="4">
+        <v>45995</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H33" s="1">
+        <v>3</v>
+      </c>
+      <c r="I33" s="1">
+        <v>947.24896666666666</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A34" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B34" s="4">
+        <v>45997</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D34" s="4">
+        <v>45997</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H34" s="1">
+        <v>1</v>
+      </c>
+      <c r="I34" s="1">
+        <v>453.54700000000003</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A35" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B35" s="4">
+        <v>45997</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D35" s="4">
+        <v>45997</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H35" s="1">
+        <v>1</v>
+      </c>
+      <c r="I35" s="1">
+        <v>453.54700000000003</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A36" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B36" s="4">
+        <v>45997</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D36" s="4">
+        <v>45997</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H36" s="1">
+        <v>20</v>
+      </c>
+      <c r="I36" s="1">
+        <v>356.285685</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A37" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B37" s="4">
+        <v>45997</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D37" s="4">
+        <v>45997</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="H37" s="1">
         <v>10</v>
       </c>
-      <c r="B2" s="2">
-        <v>45991</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="2">
-        <v>45991</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="3">
-        <v>1</v>
-      </c>
-      <c r="I2" s="3">
-        <v>71781.230100000001</v>
-      </c>
-      <c r="J2" s="1">
-        <v>1</v>
-      </c>
-      <c r="K2" s="2">
-        <v>45958</v>
+      <c r="I37" s="1">
+        <v>374.00160999999997</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A38" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B38" s="4">
+        <v>45997</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D38" s="4">
+        <v>45997</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H38" s="1">
+        <v>2</v>
+      </c>
+      <c r="I38" s="1">
+        <v>369.35230000000001</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A39" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B39" s="4">
+        <v>45999</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D39" s="4">
+        <v>45999</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H39" s="1">
+        <v>50</v>
+      </c>
+      <c r="I39" s="1">
+        <v>1250.3544340000001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A40" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B40" s="4">
+        <v>46000</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D40" s="4">
+        <v>46000</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H40" s="1">
+        <v>3</v>
+      </c>
+      <c r="I40" s="1">
+        <v>305.36250000000001</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A41" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B41" s="4">
+        <v>46000</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D41" s="4">
+        <v>46000</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H41" s="1">
+        <v>1</v>
+      </c>
+      <c r="I41" s="1">
+        <v>250.5197</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A42" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B42" s="4">
+        <v>46000</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D42" s="4">
+        <v>46000</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H42" s="1">
+        <v>3</v>
+      </c>
+      <c r="I42" s="1">
+        <v>312.14859999999999</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A43" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B43" s="4">
+        <v>46000</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D43" s="4">
+        <v>46000</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H43" s="1">
+        <v>1</v>
+      </c>
+      <c r="I43" s="1">
+        <v>255.91990000000001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A44" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B44" s="4">
+        <v>46000</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D44" s="4">
+        <v>46000</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="H44" s="1">
+        <v>3</v>
+      </c>
+      <c r="I44" s="1">
+        <v>352.56436666666667</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A45" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B45" s="4">
+        <v>46000</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D45" s="4">
+        <v>46000</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="H45" s="1">
+        <v>1</v>
+      </c>
+      <c r="I45" s="1">
+        <v>288.08150000000001</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A46" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B46" s="4">
+        <v>46000</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D46" s="4">
+        <v>46000</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="H46" s="1">
+        <v>1</v>
+      </c>
+      <c r="I46" s="1">
+        <v>149.30799999999999</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A47" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B47" s="4">
+        <v>46000</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D47" s="4">
+        <v>46000</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="H47" s="1">
+        <v>2</v>
+      </c>
+      <c r="I47" s="1">
+        <v>123.0692</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A48" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B48" s="4">
+        <v>46000</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D48" s="4">
+        <v>46000</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H48" s="1">
+        <v>1</v>
+      </c>
+      <c r="I48" s="1">
+        <v>116.9808</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A49" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B49" s="4">
+        <v>46000</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D49" s="4">
+        <v>46000</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H49" s="1">
+        <v>2</v>
+      </c>
+      <c r="I49" s="1">
+        <v>90.742000000000004</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A50" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B50" s="4">
+        <v>46000</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D50" s="4">
+        <v>46000</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="H50" s="1">
+        <v>1</v>
+      </c>
+      <c r="I50" s="1">
+        <v>76.859899999999996</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A51" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B51" s="4">
+        <v>46000</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D51" s="4">
+        <v>46000</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="H51" s="1">
+        <v>2</v>
+      </c>
+      <c r="I51" s="1">
+        <v>50.621099999999998</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A52" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B52" s="4">
+        <v>46000</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D52" s="4">
+        <v>46000</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H52" s="1">
+        <v>1</v>
+      </c>
+      <c r="I52" s="1">
+        <v>57.544899999999998</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A53" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B53" s="4">
+        <v>46000</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D53" s="4">
+        <v>46000</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H53" s="1">
+        <v>2</v>
+      </c>
+      <c r="I53" s="1">
+        <v>31.306100000000001</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A54" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B54" s="4">
+        <v>46000</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D54" s="4">
+        <v>46000</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H54" s="1">
+        <v>5</v>
+      </c>
+      <c r="I54" s="1">
+        <v>1857.01466</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A55" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B55" s="4">
+        <v>46000</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D55" s="4">
+        <v>46000</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H55" s="1">
+        <v>1</v>
+      </c>
+      <c r="I55" s="1">
+        <v>1027.8838000000001</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A56" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B56" s="4">
+        <v>46000</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D56" s="4">
+        <v>46000</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="H56" s="1">
+        <v>1</v>
+      </c>
+      <c r="I56" s="1">
+        <v>5050.4791999999998</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A57" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B57" s="4">
+        <v>46000</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D57" s="4">
+        <v>46000</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="H57" s="1">
+        <v>1</v>
+      </c>
+      <c r="I57" s="1">
+        <v>5050.4791999999998</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A58" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B58" s="4">
+        <v>46000</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D58" s="4">
+        <v>46000</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H58" s="1">
+        <v>1</v>
+      </c>
+      <c r="I58" s="1">
+        <v>1374.2901999999999</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A59" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B59" s="4">
+        <v>46000</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D59" s="4">
+        <v>46000</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H59" s="1">
+        <v>1</v>
+      </c>
+      <c r="I59" s="1">
+        <v>1336.288</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A60" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B60" s="4">
+        <v>46000</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D60" s="4">
+        <v>46000</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H60" s="1">
+        <v>1</v>
+      </c>
+      <c r="I60" s="1">
+        <v>988.65989999999999</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A61" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B61" s="4">
+        <v>46000</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D61" s="4">
+        <v>46000</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="H61" s="1">
+        <v>1</v>
+      </c>
+      <c r="I61" s="1">
+        <v>1250.7188000000001</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A62" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B62" s="4">
+        <v>46000</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D62" s="4">
+        <v>46000</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="H62" s="1">
+        <v>1</v>
+      </c>
+      <c r="I62" s="1">
+        <v>772.76049999999998</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A63" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B63" s="4">
+        <v>46000</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D63" s="4">
+        <v>46000</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H63" s="1">
+        <v>1</v>
+      </c>
+      <c r="I63" s="1">
+        <v>1027.8838000000001</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A64" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B64" s="4">
+        <v>46000</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D64" s="4">
+        <v>46000</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H64" s="1">
+        <v>1</v>
+      </c>
+      <c r="I64" s="1">
+        <v>176.1447</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A65" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B65" s="4">
+        <v>46000</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D65" s="4">
+        <v>46000</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H65" s="1">
+        <v>1</v>
+      </c>
+      <c r="I65" s="1">
+        <v>176.1448</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A66" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B66" s="4">
+        <v>46000</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D66" s="4">
+        <v>46000</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H66" s="1">
+        <v>1</v>
+      </c>
+      <c r="I66" s="1">
+        <v>197.3604</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A67" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B67" s="4">
+        <v>46000</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D67" s="4">
+        <v>46000</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H67" s="1">
+        <v>1</v>
+      </c>
+      <c r="I67" s="1">
+        <v>746.61519999999996</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A68" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B68" s="4">
+        <v>46000</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D68" s="4">
+        <v>46000</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H68" s="1">
+        <v>1</v>
+      </c>
+      <c r="I68" s="1">
+        <v>1924.0085999999999</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A69" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B69" s="4">
+        <v>46000</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D69" s="4">
+        <v>46000</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H69" s="1">
+        <v>1</v>
+      </c>
+      <c r="I69" s="1">
+        <v>4470.7187999999996</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A70" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B70" s="4">
+        <v>46000</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D70" s="4">
+        <v>46000</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H70" s="1">
+        <v>1</v>
+      </c>
+      <c r="I70" s="1">
+        <v>820.37819999999999</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A71" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B71" s="4">
+        <v>46000</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D71" s="4">
+        <v>46000</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="H71" s="1">
+        <v>1</v>
+      </c>
+      <c r="I71" s="1">
+        <v>825.44970000000001</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A72" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B72" s="4">
+        <v>46000</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D72" s="4">
+        <v>46000</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="H72" s="1">
+        <v>1</v>
+      </c>
+      <c r="I72" s="1">
+        <v>864.93449999999996</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A73" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B73" s="4">
+        <v>46000</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D73" s="4">
+        <v>46000</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H73" s="1">
+        <v>1</v>
+      </c>
+      <c r="I73" s="1">
+        <v>1555.6860999999999</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A74" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B74" s="4">
+        <v>46001</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D74" s="4">
+        <v>46001</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="H74" s="1">
+        <v>2</v>
+      </c>
+      <c r="I74" s="1">
+        <v>986.40314999999998</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A75" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B75" s="4">
+        <v>46001</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="D75" s="4">
+        <v>46001</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H75" s="1">
+        <v>1</v>
+      </c>
+      <c r="I75" s="1">
+        <v>1174.2626</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A76" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B76" s="4">
+        <v>46001</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D76" s="4">
+        <v>46001</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="H76" s="1">
+        <v>1</v>
+      </c>
+      <c r="I76" s="1">
+        <v>1679.9862000000001</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A77" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B77" s="4">
+        <v>46001</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D77" s="4">
+        <v>46001</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="H77" s="1">
+        <v>1</v>
+      </c>
+      <c r="I77" s="1">
+        <v>2515.7188000000001</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A78" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B78" s="4">
+        <v>46001</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D78" s="4">
+        <v>46001</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="H78" s="1">
+        <v>1</v>
+      </c>
+      <c r="I78" s="1">
+        <v>3665.7188000000001</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A79" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B79" s="4">
+        <v>46001</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D79" s="4">
+        <v>46001</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="H79" s="1">
+        <v>10</v>
+      </c>
+      <c r="I79" s="1">
+        <v>66.37612</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A80" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B80" s="4">
+        <v>46001</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D80" s="4">
+        <v>46001</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="H80" s="1">
+        <v>10</v>
+      </c>
+      <c r="I80" s="1">
+        <v>417.77080999999998</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A81" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B81" s="4">
+        <v>46001</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D81" s="4">
+        <v>46001</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H81" s="1">
+        <v>10</v>
+      </c>
+      <c r="I81" s="1">
+        <v>288.94436999999999</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A82" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B82" s="4">
+        <v>46001</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D82" s="4">
+        <v>46001</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="H82" s="1">
+        <v>10</v>
+      </c>
+      <c r="I82" s="1">
+        <v>182.93473</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A83" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B83" s="4">
+        <v>46001</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D83" s="4">
+        <v>46001</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H83" s="1">
+        <v>10</v>
+      </c>
+      <c r="I83" s="1">
+        <v>64.945099999999996</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A84" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B84" s="4">
+        <v>46001</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D84" s="4">
+        <v>46001</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="H84" s="1">
+        <v>10</v>
+      </c>
+      <c r="I84" s="1">
+        <v>141.71293</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A85" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B85" s="4">
+        <v>46002</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D85" s="4">
+        <v>46002</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="H85" s="1">
+        <v>2</v>
+      </c>
+      <c r="I85" s="1">
+        <v>112.5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A86" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B86" s="4">
+        <v>46002</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D86" s="4">
+        <v>46002</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="H86" s="1">
+        <v>8</v>
+      </c>
+      <c r="I86" s="1">
+        <v>1021.23275</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A87" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B87" s="4">
+        <v>46002</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D87" s="4">
+        <v>46002</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="H87" s="1">
+        <v>1</v>
+      </c>
+      <c r="I87" s="1">
+        <v>1048.4792</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A88" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B88" s="4">
+        <v>46002</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D88" s="4">
+        <v>46002</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H88" s="1">
+        <v>1</v>
+      </c>
+      <c r="I88" s="1">
+        <v>1027.8838000000001</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A89" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B89" s="4">
+        <v>46002</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D89" s="4">
+        <v>46002</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="H89" s="1">
+        <v>1</v>
+      </c>
+      <c r="I89" s="1">
+        <v>616.125</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A90" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B90" s="4">
+        <v>46003</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="D90" s="4">
+        <v>46003</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H90" s="1">
+        <v>1</v>
+      </c>
+      <c r="I90" s="1">
+        <v>2758.2253000000001</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A91" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B91" s="4">
+        <v>46003</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D91" s="4">
+        <v>46003</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="H91" s="1">
+        <v>10</v>
+      </c>
+      <c r="I91" s="1">
+        <v>155.75871999999998</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A92" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B92" s="4">
+        <v>46004</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D92" s="4">
+        <v>46004</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="H92" s="1">
+        <v>20</v>
+      </c>
+      <c r="I92" s="1">
+        <v>551.51608999999996</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A93" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B93" s="4">
+        <v>46004</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D93" s="4">
+        <v>46004</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="H93" s="1">
+        <v>20</v>
+      </c>
+      <c r="I93" s="1">
+        <v>1007.574705</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A94" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B94" s="4">
+        <v>46004</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D94" s="4">
+        <v>46004</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="H94" s="1">
+        <v>7</v>
+      </c>
+      <c r="I94" s="1">
+        <v>178.57212857142855</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A95" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B95" s="4">
+        <v>46004</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D95" s="4">
+        <v>46004</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="H95" s="1">
+        <v>10</v>
+      </c>
+      <c r="I95" s="1">
+        <v>95.361720000000005</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A96" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B96" s="4">
+        <v>46006</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D96" s="4">
+        <v>46006</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="H96" s="1">
+        <v>30</v>
+      </c>
+      <c r="I96" s="1">
+        <v>944.18813999999998</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A97" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B97" s="4">
+        <v>46006</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D97" s="4">
+        <v>46006</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="H97" s="1">
+        <v>4</v>
+      </c>
+      <c r="I97" s="1">
+        <v>603.31955000000005</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A98" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B98" s="4">
+        <v>46006</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D98" s="4">
+        <v>46006</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="H98" s="1">
+        <v>3</v>
+      </c>
+      <c r="I98" s="1">
+        <v>442.52006666666665</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A99" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B99" s="4">
+        <v>46006</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D99" s="4">
+        <v>46006</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="H99" s="1">
+        <v>30</v>
+      </c>
+      <c r="I99" s="1">
+        <v>944.18813999999998</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A100" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B100" s="4">
+        <v>46006</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D100" s="4">
+        <v>46006</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="H100" s="1">
+        <v>4</v>
+      </c>
+      <c r="I100" s="1">
+        <v>603.31955000000005</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A101" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B101" s="4">
+        <v>46006</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D101" s="4">
+        <v>46006</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="H101" s="1">
+        <v>3</v>
+      </c>
+      <c r="I101" s="1">
+        <v>442.52006666666665</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A102" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B102" s="4">
+        <v>46006</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D102" s="4">
+        <v>46006</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G102" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="H102" s="1">
+        <v>1</v>
+      </c>
+      <c r="I102" s="1">
+        <v>115.7302</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A103" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B103" s="4">
+        <v>46006</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D103" s="4">
+        <v>46006</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="H103" s="1">
+        <v>3</v>
+      </c>
+      <c r="I103" s="1">
+        <v>186.39183333333335</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A104" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B104" s="4">
+        <v>46007</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="D104" s="4">
+        <v>46007</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="H104" s="1">
+        <v>10</v>
+      </c>
+      <c r="I104" s="1">
+        <v>138.97314</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A105" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B105" s="4">
+        <v>46007</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D105" s="4">
+        <v>46007</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="H105" s="1">
+        <v>10</v>
+      </c>
+      <c r="I105" s="1">
+        <v>126.2123</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A106" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B106" s="4">
+        <v>46008</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D106" s="4">
+        <v>46008</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="H106" s="1">
+        <v>20</v>
+      </c>
+      <c r="I106" s="1">
+        <v>112.5</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A107" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B107" s="4">
+        <v>46008</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D107" s="4">
+        <v>46008</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G107" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="H107" s="1">
+        <v>1</v>
+      </c>
+      <c r="I107" s="1">
+        <v>571.43740000000003</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A108" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B108" s="4">
+        <v>46008</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="D108" s="4">
+        <v>46008</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G108" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="H108" s="1">
+        <v>1</v>
+      </c>
+      <c r="I108" s="1">
+        <v>616.94839999999999</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A109" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B109" s="4">
+        <v>46008</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D109" s="4">
+        <v>46008</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G109" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H109" s="1">
+        <v>1</v>
+      </c>
+      <c r="I109" s="1">
+        <v>421.50279999999998</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A110" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B110" s="4">
+        <v>46008</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D110" s="4">
+        <v>46008</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G110" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H110" s="1">
+        <v>1</v>
+      </c>
+      <c r="I110" s="1">
+        <v>531.91790000000003</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A111" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B111" s="4">
+        <v>46008</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D111" s="4">
+        <v>46008</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G111" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H111" s="1">
+        <v>1</v>
+      </c>
+      <c r="I111" s="1">
+        <v>531.91790000000003</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A112" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B112" s="4">
+        <v>46008</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D112" s="4">
+        <v>46008</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G112" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="H112" s="1">
+        <v>1</v>
+      </c>
+      <c r="I112" s="1">
+        <v>876.5847</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A113" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B113" s="4">
+        <v>46008</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D113" s="4">
+        <v>46008</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G113" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="H113" s="1">
+        <v>1</v>
+      </c>
+      <c r="I113" s="1">
+        <v>2186.8652000000002</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A114" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B114" s="4">
+        <v>46008</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="D114" s="4">
+        <v>46008</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G114" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="H114" s="1">
+        <v>1</v>
+      </c>
+      <c r="I114" s="1">
+        <v>971.83019999999999</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A115" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B115" s="4">
+        <v>46008</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D115" s="4">
+        <v>46008</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G115" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="H115" s="1">
+        <v>1</v>
+      </c>
+      <c r="I115" s="1">
+        <v>408.47919999999999</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A116" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B116" s="4">
+        <v>46008</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D116" s="4">
+        <v>46008</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G116" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H116" s="1">
+        <v>1</v>
+      </c>
+      <c r="I116" s="1">
+        <v>341.40980000000002</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A117" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B117" s="4">
+        <v>46008</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D117" s="4">
+        <v>46008</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G117" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="H117" s="1">
+        <v>4</v>
+      </c>
+      <c r="I117" s="1">
+        <v>2293.9116749999998</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A118" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B118" s="4">
+        <v>46008</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="D118" s="4">
+        <v>46008</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G118" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="H118" s="1">
+        <v>2</v>
+      </c>
+      <c r="I118" s="1">
+        <v>2293.91165</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A119" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B119" s="4">
+        <v>46008</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D119" s="4">
+        <v>46008</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G119" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="H119" s="1">
+        <v>2</v>
+      </c>
+      <c r="I119" s="1">
+        <v>2934.3334</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A120" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B120" s="4">
+        <v>46008</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="D120" s="4">
+        <v>46008</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G120" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="H120" s="1">
+        <v>2</v>
+      </c>
+      <c r="I120" s="1">
+        <v>2886.6614500000001</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A121" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B121" s="4">
+        <v>46008</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D121" s="4">
+        <v>46008</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G121" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="H121" s="1">
+        <v>1</v>
+      </c>
+      <c r="I121" s="1">
+        <v>1004.2337</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A122" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B122" s="4">
+        <v>46008</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D122" s="4">
+        <v>46008</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G122" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="H122" s="1">
+        <v>1</v>
+      </c>
+      <c r="I122" s="1">
+        <v>1122.6095</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A123" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B123" s="4">
+        <v>46008</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D123" s="4">
+        <v>46008</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G123" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H123" s="1">
+        <v>3</v>
+      </c>
+      <c r="I123" s="1">
+        <v>948.47920000000011</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A124" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B124" s="4">
+        <v>46008</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="D124" s="4">
+        <v>46008</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G124" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="H124" s="1">
+        <v>3</v>
+      </c>
+      <c r="I124" s="1">
+        <v>1049.3905</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A125" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B125" s="4">
+        <v>46008</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="D125" s="4">
+        <v>46008</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G125" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H125" s="1">
+        <v>1</v>
+      </c>
+      <c r="I125" s="1">
+        <v>945.74530000000004</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A126" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B126" s="4">
+        <v>46008</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="D126" s="4">
+        <v>46008</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G126" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="H126" s="1">
+        <v>1</v>
+      </c>
+      <c r="I126" s="1">
+        <v>9750.9771000000001</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A127" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B127" s="4">
+        <v>46008</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D127" s="4">
+        <v>46008</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G127" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="H127" s="1">
+        <v>1</v>
+      </c>
+      <c r="I127" s="1">
+        <v>2323.433</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A128" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B128" s="4">
+        <v>46008</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="D128" s="4">
+        <v>46008</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G128" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H128" s="1">
+        <v>1</v>
+      </c>
+      <c r="I128" s="1">
+        <v>1339.9848999999999</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A129" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B129" s="4">
+        <v>46008</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="D129" s="4">
+        <v>46008</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G129" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="H129" s="1">
+        <v>1</v>
+      </c>
+      <c r="I129" s="1">
+        <v>2276.4848999999999</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A130" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B130" s="4">
+        <v>46008</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D130" s="4">
+        <v>46008</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F130" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G130" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="H130" s="1">
+        <v>100</v>
+      </c>
+      <c r="I130" s="1">
+        <v>281.17033200000003</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A131" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B131" s="4">
+        <v>46009</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="D131" s="4">
+        <v>46009</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G131" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="H131" s="1">
+        <v>1</v>
+      </c>
+      <c r="I131" s="1">
+        <v>3763.4110000000001</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A132" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B132" s="4">
+        <v>46009</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="D132" s="4">
+        <v>46009</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F132" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G132" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="H132" s="1">
+        <v>51</v>
+      </c>
+      <c r="I132" s="1">
+        <v>901.84511568627443</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A133" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B133" s="4">
+        <v>46009</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D133" s="4">
+        <v>46009</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G133" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="H133" s="1">
+        <v>6</v>
+      </c>
+      <c r="I133" s="1">
+        <v>2254.5071499999999</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A134" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B134" s="4">
+        <v>46009</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="D134" s="4">
+        <v>46009</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G134" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="H134" s="1">
+        <v>98</v>
+      </c>
+      <c r="I134" s="1">
+        <v>178.55976530612244</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A135" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B135" s="4">
+        <v>46009</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D135" s="4">
+        <v>46009</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G135" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="H135" s="1">
+        <v>10</v>
+      </c>
+      <c r="I135" s="1">
+        <v>331.3623</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A136" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B136" s="4">
+        <v>46009</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="D136" s="4">
+        <v>46009</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G136" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="H136" s="1">
+        <v>5</v>
+      </c>
+      <c r="I136" s="1">
+        <v>118.0151</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A137" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B137" s="4">
+        <v>46010</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="D137" s="4">
+        <v>46010</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G137" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="H137" s="1">
+        <v>1</v>
+      </c>
+      <c r="I137" s="1">
+        <v>759.83500000000004</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A138" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B138" s="4">
+        <v>46010</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="D138" s="4">
+        <v>46010</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G138" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H138" s="1">
+        <v>1</v>
+      </c>
+      <c r="I138" s="1">
+        <v>531.91790000000003</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A139" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B139" s="4">
+        <v>46010</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D139" s="4">
+        <v>46010</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F139" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G139" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="H139" s="1">
+        <v>3</v>
+      </c>
+      <c r="I139" s="1">
+        <v>222.25443333333331</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A140" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B140" s="4">
+        <v>46010</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="D140" s="4">
+        <v>46010</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G140" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="H140" s="1">
+        <v>1</v>
+      </c>
+      <c r="I140" s="1">
+        <v>895.47919999999999</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A141" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B141" s="4">
+        <v>46010</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="D141" s="4">
+        <v>46010</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F141" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G141" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="H141" s="1">
+        <v>1</v>
+      </c>
+      <c r="I141" s="1">
+        <v>2944.4992999999999</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A142" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B142" s="4">
+        <v>46010</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="D142" s="4">
+        <v>46010</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G142" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="H142" s="1">
+        <v>1</v>
+      </c>
+      <c r="I142" s="1">
+        <v>4185.5339999999997</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A143" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B143" s="4">
+        <v>46010</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="D143" s="4">
+        <v>46010</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F143" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G143" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="H143" s="1">
+        <v>30</v>
+      </c>
+      <c r="I143" s="1">
+        <v>3124.1662933333337</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A144" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B144" s="4">
+        <v>46010</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="D144" s="4">
+        <v>46010</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G144" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="H144" s="1">
+        <v>1</v>
+      </c>
+      <c r="I144" s="1">
+        <v>485.5575</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A145" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B145" s="4">
+        <v>46010</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="D145" s="4">
+        <v>46010</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F145" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G145" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="H145" s="1">
+        <v>1</v>
+      </c>
+      <c r="I145" s="1">
+        <v>903.3279</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A146" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B146" s="4">
+        <v>46010</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D146" s="4">
+        <v>46010</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F146" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G146" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="H146" s="1">
+        <v>1</v>
+      </c>
+      <c r="I146" s="1">
+        <v>884.23159999999996</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A147" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B147" s="4">
+        <v>46010</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="D147" s="4">
+        <v>46010</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G147" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H147" s="1">
+        <v>1</v>
+      </c>
+      <c r="I147" s="1">
+        <v>1027.8838000000001</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A148" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B148" s="4">
+        <v>46010</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="D148" s="4">
+        <v>46010</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F148" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G148" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="H148" s="1">
+        <v>1</v>
+      </c>
+      <c r="I148" s="1">
+        <v>1012.8807</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A149" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B149" s="4">
+        <v>46010</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="D149" s="4">
+        <v>46010</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G149" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="H149" s="1">
+        <v>1</v>
+      </c>
+      <c r="I149" s="1">
+        <v>946.66120000000001</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A150" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B150" s="4">
+        <v>46010</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="D150" s="4">
+        <v>46010</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G150" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="H150" s="1">
+        <v>1</v>
+      </c>
+      <c r="I150" s="1">
+        <v>1015.4424</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A151" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B151" s="4">
+        <v>46010</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D151" s="4">
+        <v>46010</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F151" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G151" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="H151" s="1">
+        <v>1</v>
+      </c>
+      <c r="I151" s="1">
+        <v>4044.4286999999999</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A152" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B152" s="4">
+        <v>46010</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D152" s="4">
+        <v>46010</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F152" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G152" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H152" s="1">
+        <v>1</v>
+      </c>
+      <c r="I152" s="1">
+        <v>1663.2928999999999</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A153" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B153" s="4">
+        <v>46010</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D153" s="4">
+        <v>46010</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F153" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G153" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="H153" s="1">
+        <v>1</v>
+      </c>
+      <c r="I153" s="1">
+        <v>1718.6865</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A154" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B154" s="4">
+        <v>46010</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="D154" s="4">
+        <v>46010</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F154" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G154" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="H154" s="1">
+        <v>1</v>
+      </c>
+      <c r="I154" s="1">
+        <v>1973.7138</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A155" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B155" s="4">
+        <v>46010</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="D155" s="4">
+        <v>46010</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F155" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G155" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="H155" s="1">
+        <v>1</v>
+      </c>
+      <c r="I155" s="1">
+        <v>2315.7188000000001</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A156" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B156" s="4">
+        <v>46011</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="D156" s="4">
+        <v>46011</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F156" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G156" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="H156" s="1">
+        <v>1</v>
+      </c>
+      <c r="I156" s="1">
+        <v>2671.4724000000001</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A157" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B157" s="4">
+        <v>46013</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="D157" s="4">
+        <v>46013</v>
+      </c>
+      <c r="E157" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F157" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G157" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="H157" s="1">
+        <v>4</v>
+      </c>
+      <c r="I157" s="1">
+        <v>1444.6440250000001</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A158" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B158" s="4">
+        <v>46014</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D158" s="4">
+        <v>46014</v>
+      </c>
+      <c r="E158" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F158" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G158" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="H158" s="1">
+        <v>10</v>
+      </c>
+      <c r="I158" s="1">
+        <v>331.31545</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A159" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B159" s="4">
+        <v>46015</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="D159" s="4">
+        <v>46015</v>
+      </c>
+      <c r="E159" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F159" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G159" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="H159" s="1">
+        <v>1</v>
+      </c>
+      <c r="I159" s="1">
+        <v>2132.3506000000002</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A160" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B160" s="4">
+        <v>46015</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="D160" s="4">
+        <v>46015</v>
+      </c>
+      <c r="E160" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F160" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G160" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="H160" s="1">
+        <v>10</v>
+      </c>
+      <c r="I160" s="1">
+        <v>349.03899999999999</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A161" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B161" s="4">
+        <v>46015</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="D161" s="4">
+        <v>46015</v>
+      </c>
+      <c r="E161" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F161" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G161" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="H161" s="1">
+        <v>5</v>
+      </c>
+      <c r="I161" s="1">
+        <v>422.18991999999997</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>